--- a/output/2026-10-04_12_Malesia_Sarawak_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-04_12_Malesia_Sarawak_Depolverazione_Trattamento_aria.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda reale confermata (fondata 1961, CIDB G7, ISO 9001:2015). Contractor M&amp;E che progetta/installa/commissiona sistemi HVAC e ventilazione meccanica per impianti industriali (semiconduttori, LNG, ospedali). Non e' uno specialista puro di dust collection, ma rientra nel perimetro 'trattamento aria' come partner commerciale B2B (non cliente finale). Sede Sibu confermata: 23 Jalan Bengkel, Pekan Sibu; sede Kuching confermata: Lots 228-229, Section 49, KTLD, Jalan Tunku Abdul Rahman. Fonti: sito ufficiale pansar.com.my e ricerche indipendenti.</t>
+          <t>Azienda reale confermata (fondata 1961, CIDB G7, ISO 9001:2015). Contractor M&amp;E che progetta/installa/commissiona sistemi HVAC e ventilazione meccanica per impianti industriali (semiconduttori, LNG, ospedali). Non e' uno specialista puro di dust collection, ma rientra nel perimetro 'trattamento aria' come partner commerciale B2B (non cliente finale). Sede Sibu confermata: 23 Jalan Bengkel, Pekan Sibu; sede Kuching confermata: Lots 228-229, Section 49, KTLD, Jalan Tunku Abdul Rahman. Fonti: sito ufficiale pansar.com.my e ricerche indipendenti. [DUPLICATO — vedi anche: 2026-10-04_11_Malesia_Sarawak_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
